--- a/service/templates/Report_simple.xlsx
+++ b/service/templates/Report_simple.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Лист1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Лист1!$B$2:$W$78</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Лист1!$B$2:$W$79</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="41">
   <si>
     <t xml:space="preserve">Проект</t>
   </si>
@@ -265,7 +265,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -274,7 +274,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -282,11 +282,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -303,10 +299,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -437,7 +429,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.18"/>
@@ -465,560 +457,572 @@
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="6" t="s">
+      <c r="A2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="8"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="9"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="8"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
+      <c r="A4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="9"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6" t="s">
+      <c r="A5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="9"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="6" t="s">
+      <c r="A6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="9"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="9"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="6" t="s">
+      <c r="A8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="9"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="s">
+      <c r="A9" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="9"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="6" t="s">
+      <c r="A10" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="9"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="9"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="9"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="6" t="s">
+      <c r="A13" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="9"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="8"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="6" t="s">
+      <c r="A14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="9"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="8"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" s="6" t="s">
+      <c r="A15" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="9"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="6" t="s">
+      <c r="A16" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="9"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" s="6" t="s">
+      <c r="A17" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="9"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" s="6" t="s">
+      <c r="A18" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="9"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B19" s="6" t="s">
+      <c r="A19" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="9"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="8"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B20" s="6" t="s">
+      <c r="A20" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="9"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="8"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B21" s="6" t="s">
+      <c r="A21" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="9"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="8"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B22" s="6" t="s">
+      <c r="A22" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="9"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" s="6" t="s">
+      <c r="A23" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="9"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="8"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B24" s="6" t="s">
+      <c r="A24" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="9"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="8"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B25" s="6" t="s">
+      <c r="A25" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="9"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="8"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B26" s="6" t="s">
+      <c r="A26" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="9"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="8"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B27" s="6" t="s">
+      <c r="A27" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="9"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="8"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B28" s="6" t="s">
+      <c r="A28" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="9"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="8"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B29" s="6" t="s">
+      <c r="A29" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="9"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="8"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B30" s="6" t="s">
+      <c r="A30" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="9"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="8"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B31" s="6" t="s">
+      <c r="A31" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="9"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="8"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B32" s="6" t="s">
+      <c r="A32" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="9"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="8"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B33" s="6" t="s">
+      <c r="A33" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="9"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="8"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B34" s="6" t="s">
+      <c r="A34" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="8"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="9"/>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B35" s="6" t="s">
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="8"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="9"/>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B36" s="6" t="s">
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="8"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="9"/>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="8"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="10"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="10"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="10"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="10"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
+      <c r="A42" s="9"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="10"/>
-      <c r="B43" s="11"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
+      <c r="A43" s="9"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="10"/>
-      <c r="B44" s="11"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
+      <c r="A44" s="9"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="10"/>
-      <c r="B45" s="11"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="11"/>
+      <c r="A45" s="9"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="10"/>
-      <c r="B46" s="11"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
+      <c r="A46" s="9"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="10"/>
-      <c r="B47" s="11"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="11"/>
-      <c r="G47" s="11"/>
+      <c r="A47" s="9"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="10"/>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="11"/>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="A48" s="9"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="9"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9"/>
+    </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -1041,6 +1045,7 @@
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:F1"/>

--- a/service/templates/Report_simple.xlsx
+++ b/service/templates/Report_simple.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Лист1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Лист1!$B$2:$W$79</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Лист1!$A$1:$H$46</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -429,14 +429,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="4.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="25.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="17.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="14.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="13.35"/>
@@ -946,6 +947,9 @@
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9"/>
@@ -1010,19 +1014,11 @@
       <c r="F48" s="9"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="9"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -1045,14 +1041,13 @@
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:F1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.39375" right="0.274305555555556" top="0.39375" bottom="0.39375" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="129" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="137" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/service/templates/Report_simple.xlsx
+++ b/service/templates/Report_simple.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Лист1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Лист1!$A$1:$H$46</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Лист1!$A$1:$H$47</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="42">
   <si>
     <t xml:space="preserve">Проект</t>
   </si>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t xml:space="preserve">Основная сборка + артефакты Draft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Перезапуск службы сервера 1С</t>
   </si>
   <si>
     <t xml:space="preserve">Обновление базы 1С (RU)</t>
@@ -429,10 +432,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="4.87"/>
@@ -540,7 +543,7 @@
       <c r="F7" s="7"/>
       <c r="G7" s="8"/>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
         <v>3</v>
       </c>
@@ -553,7 +556,7 @@
       <c r="F8" s="7"/>
       <c r="G8" s="8"/>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
         <v>3</v>
       </c>
@@ -581,7 +584,7 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>13</v>
@@ -607,7 +610,7 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>15</v>
@@ -880,10 +883,10 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
@@ -893,7 +896,7 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>36</v>
@@ -930,29 +933,33 @@
       <c r="F37" s="7"/>
       <c r="G37" s="8"/>
     </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="8"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-    </row>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="9"/>
+      <c r="A42" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
@@ -1014,11 +1021,19 @@
       <c r="F48" s="9"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="9"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9"/>
+    </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -1041,6 +1056,7 @@
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:F1"/>

--- a/service/templates/Report_simple.xlsx
+++ b/service/templates/Report_simple.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -11,7 +11,7 @@
     <sheet name="Лист1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Лист1!$A$1:$H$47</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Лист1!$A$1:$H$48</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="44">
   <si>
     <t xml:space="preserve">Проект</t>
   </si>
@@ -37,12 +37,15 @@
     <t xml:space="preserve">Oint</t>
   </si>
   <si>
-    <t xml:space="preserve">Смена версии и создание драфта на GitHub</t>
+    <t xml:space="preserve">Смена версии (в т.ч. Melezh в jf) и создание драфта</t>
   </si>
   <si>
     <t xml:space="preserve">Melezh</t>
   </si>
   <si>
+    <t xml:space="preserve">Смена версии (в т.ч. Oint зависимости) и создание драфта</t>
+  </si>
+  <si>
     <t xml:space="preserve">Основная сборка проекта</t>
   </si>
   <si>
@@ -67,7 +70,7 @@
     <t xml:space="preserve">Сборка релиза и загрузка артефактов в Draft</t>
   </si>
   <si>
-    <t xml:space="preserve">Создание docker-образов</t>
+    <t xml:space="preserve">Создание docker-образов (тест)</t>
   </si>
   <si>
     <t xml:space="preserve">Полное тестирование</t>
@@ -122,6 +125,9 @@
   </si>
   <si>
     <t xml:space="preserve">Тестовый деплой документации</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Создание docker-образов (релиз)</t>
   </si>
   <si>
     <t xml:space="preserve">Основной деплой документации (RU)</t>
@@ -432,7 +438,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.49"/>
@@ -483,7 +489,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -496,7 +502,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
@@ -509,7 +515,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
@@ -522,7 +528,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
@@ -535,7 +541,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
@@ -548,7 +554,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -561,7 +567,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
@@ -574,7 +580,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
@@ -587,7 +593,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
@@ -600,7 +606,7 @@
         <v>5</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
@@ -613,7 +619,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -626,7 +632,7 @@
         <v>3</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -639,7 +645,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -652,7 +658,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -665,7 +671,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
@@ -678,7 +684,7 @@
         <v>3</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -691,7 +697,7 @@
         <v>3</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
@@ -704,7 +710,7 @@
         <v>3</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
@@ -717,7 +723,7 @@
         <v>3</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
@@ -730,7 +736,7 @@
         <v>3</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
@@ -743,7 +749,7 @@
         <v>3</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
@@ -756,7 +762,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
@@ -769,7 +775,7 @@
         <v>3</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
@@ -782,7 +788,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
@@ -795,7 +801,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
@@ -808,7 +814,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
@@ -821,7 +827,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
@@ -834,7 +840,7 @@
         <v>3</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
@@ -844,10 +850,10 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
@@ -860,7 +866,7 @@
         <v>3</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
@@ -873,7 +879,7 @@
         <v>3</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
@@ -886,7 +892,7 @@
         <v>3</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
@@ -896,10 +902,10 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
@@ -909,10 +915,10 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
@@ -925,7 +931,7 @@
         <v>3</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
@@ -938,7 +944,7 @@
         <v>3</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
@@ -946,29 +952,33 @@
       <c r="F38" s="7"/>
       <c r="G38" s="8"/>
     </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-    </row>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="8"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="9"/>
+      <c r="A43" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
@@ -1030,11 +1040,19 @@
       <c r="F49" s="9"/>
       <c r="G49" s="9"/>
     </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="9"/>
+      <c r="B50" s="9"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="9"/>
+      <c r="G50" s="9"/>
+    </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -1057,6 +1075,7 @@
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:F1"/>

--- a/service/templates/Report_simple.xlsx
+++ b/service/templates/Report_simple.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -11,7 +11,7 @@
     <sheet name="Лист1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Лист1!$A$1:$H$48</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Лист1!$A$1:$H$35</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="32">
   <si>
     <t xml:space="preserve">Проект</t>
   </si>
@@ -37,112 +37,76 @@
     <t xml:space="preserve">Oint</t>
   </si>
   <si>
-    <t xml:space="preserve">Смена версии (в т.ч. Melezh в jf) и создание драфта</t>
+    <t xml:space="preserve">Основная сборка проекта</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Анализ SonarQube и правка замечаний</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Запустить Общее | Полное обновление и сборка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тестирование 1С (RU)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тестирование CLI (Win, RU)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тестирование OneScript (Win, RU)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тестирование 1С (EN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тестирование CLI (Deb, RU)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тестирование OneScript (RPM, EN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тестирование CLI (RPM, EN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тестирование OneScript (Win, EN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тестирование CLI (Deb, EN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тестирование OneScript (Deb, RU)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тестирование OneScript (Deb, EN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тестирование CLI (RPM, RU)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тестирование OneScript (RPM, RU)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тестирование CLI (Win, EN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Анализ результатов тестирования в ReportPortal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Повторная сборка, обновление данных для документации</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тестовый деплой документации</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Смена тега в драфте</t>
   </si>
   <si>
     <t xml:space="preserve">Melezh</t>
   </si>
   <si>
-    <t xml:space="preserve">Смена версии (в т.ч. Oint зависимости) и создание драфта</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Основная сборка проекта</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Анализ SonarQube и правка замечаний</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Основная сборка проекта после SQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Основная сборка + артефакты Draft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Перезапуск службы сервера 1С</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Обновление базы 1С (RU)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Обновление базы 1С (EN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сборка релиза и загрузка артефактов в Draft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Создание docker-образов (тест)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Полное тестирование</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тестирование 1С (RU)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тестирование CLI (Win, RU)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тестирование OneScript (Win, RU)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тестирование 1С (EN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тестирование CLI (Deb, RU)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тестирование OneScript (RPM, EN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тестирование CLI (RPM, EN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тестирование OneScript (Win, EN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тестирование CLI (Deb, EN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тестирование OneScript (Deb, RU)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тестирование OneScript (Deb, EN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тестирование CLI (RPM, RU)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тестирование OneScript (RPM, RU)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тестирование CLI (Win, EN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Анализ результатов тестирования в ReportPortal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Повторная сборка, обновление данных для документации</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тестовый деплой документации</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Создание docker-образов (релиз)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Основной деплой документации (RU)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Основной деплой документации (EN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Релиз GitHub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Пуш в OPM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Обновление на SourceForge</t>
+    <t xml:space="preserve">Запустить Общее | Публикация релиза</t>
   </si>
   <si>
     <t xml:space="preserve">Обновление Readme (RU)</t>
@@ -205,7 +169,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="10">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -242,6 +206,34 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
+      <left style="hair"/>
+      <right style="hair"/>
+      <top style="hair"/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="hair"/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="hair"/>
+      <right/>
+      <top style="hair"/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="hair"/>
+      <top style="hair"/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -274,7 +266,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -311,7 +303,55 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -335,37 +375,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -438,7 +478,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.49"/>
@@ -471,7 +511,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -484,12 +524,12 @@
       <c r="F2" s="7"/>
       <c r="G2" s="8"/>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>6</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -498,37 +538,33 @@
       <c r="G3" s="8"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="8"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="11"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="8"/>
+      <c r="A5" s="12"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
@@ -538,10 +574,10 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
@@ -554,7 +590,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -562,12 +598,12 @@
       <c r="F8" s="7"/>
       <c r="G8" s="8"/>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
@@ -580,7 +616,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
@@ -593,7 +629,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
@@ -603,10 +639,10 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
@@ -616,10 +652,10 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -632,7 +668,7 @@
         <v>3</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -645,7 +681,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -658,7 +694,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -671,7 +707,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
@@ -684,7 +720,7 @@
         <v>3</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -697,7 +733,7 @@
         <v>3</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
@@ -710,7 +746,7 @@
         <v>3</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
@@ -719,24 +755,20 @@
       <c r="G20" s="8"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="8"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
@@ -749,7 +781,7 @@
         <v>3</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
@@ -762,7 +794,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
@@ -772,10 +804,10 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
@@ -784,24 +816,24 @@
       <c r="G25" s="8"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="8"/>
+      <c r="A26" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="11"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
@@ -814,7 +846,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
@@ -822,237 +854,73 @@
       <c r="F28" s="7"/>
       <c r="G28" s="8"/>
     </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="8"/>
-    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="8"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="8"/>
-    </row>
+      <c r="A30" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="8"/>
+      <c r="A32" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="8"/>
+      <c r="A33" s="21"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="8"/>
+      <c r="A34" s="21"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="8"/>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="8"/>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="8"/>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="8"/>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="8"/>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-    </row>
+      <c r="A35" s="21"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="9"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-    </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="9"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-    </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="9"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-    </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="9"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-    </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="9"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="9"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="9"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -1061,24 +929,10 @@
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B4:F4"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.39375" right="0.274305555555556" top="0.39375" bottom="0.39375" header="0.511811023622047" footer="0.511811023622047"/>

--- a/service/templates/Report_simple.xlsx
+++ b/service/templates/Report_simple.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Лист1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Лист1!$A$1:$H$35</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Лист1!$A$1:$H$38</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="38">
   <si>
     <t xml:space="preserve">Проект</t>
   </si>
@@ -40,6 +40,9 @@
     <t xml:space="preserve">Основная сборка проекта</t>
   </si>
   <si>
+    <t xml:space="preserve">Подготовка</t>
+  </si>
+  <si>
     <t xml:space="preserve">Анализ SonarQube и правка замечаний</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t xml:space="preserve">Тестирование 1С (RU)</t>
   </si>
   <si>
+    <t xml:space="preserve">Тестирование</t>
+  </si>
+  <si>
     <t xml:space="preserve">Тестирование CLI (Win, RU)</t>
   </si>
   <si>
@@ -97,16 +103,28 @@
     <t xml:space="preserve">Повторная сборка, обновление данных для документации</t>
   </si>
   <si>
+    <t xml:space="preserve">Доки</t>
+  </si>
+  <si>
     <t xml:space="preserve">Тестовый деплой документации</t>
   </si>
   <si>
     <t xml:space="preserve">Смена тега в драфте</t>
   </si>
   <si>
+    <t xml:space="preserve">Теги</t>
+  </si>
+  <si>
     <t xml:space="preserve">Melezh</t>
   </si>
   <si>
     <t xml:space="preserve">Запустить Общее | Публикация релиза</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Релиз</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Опубликовать релиз GitHub</t>
   </si>
   <si>
     <t xml:space="preserve">Обновление Readme (RU)</t>
@@ -128,7 +146,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -160,6 +178,18 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -169,7 +199,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="8">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -206,31 +236,17 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="hair"/>
+      <left style="thin"/>
       <right style="hair"/>
-      <top style="hair"/>
-      <bottom style="hair"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top style="hair"/>
-      <bottom style="hair"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="hair"/>
-      <right/>
-      <top style="hair"/>
-      <bottom style="hair"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="hair"/>
-      <top style="hair"/>
-      <bottom style="hair"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
@@ -266,7 +282,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -303,15 +319,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="255" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -319,12 +339,12 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="255" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -339,19 +359,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -478,7 +502,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.49"/>
@@ -487,6 +511,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="4.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="4.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="17.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="14.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="13.35"/>
@@ -523,40 +548,45 @@
       <c r="E2" s="6"/>
       <c r="F2" s="7"/>
       <c r="G2" s="8"/>
+      <c r="H2" s="9" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
       <c r="F3" s="7"/>
       <c r="G3" s="8"/>
+      <c r="H3" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="10" t="s">
+      <c r="A4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="11"/>
+      <c r="B4" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
       <c r="G5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -564,351 +594,410 @@
         <v>3</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
       <c r="F6" s="7"/>
       <c r="G6" s="8"/>
+      <c r="H6" s="15" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="7"/>
       <c r="G7" s="8"/>
+      <c r="H7" s="15"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="7"/>
       <c r="G8" s="8"/>
+      <c r="H8" s="15"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
       <c r="F9" s="7"/>
       <c r="G9" s="8"/>
+      <c r="H9" s="15"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
       <c r="F10" s="7"/>
       <c r="G10" s="8"/>
+      <c r="H10" s="15"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
       <c r="F11" s="7"/>
       <c r="G11" s="8"/>
+      <c r="H11" s="15"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
       <c r="F12" s="7"/>
       <c r="G12" s="8"/>
+      <c r="H12" s="15"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="7"/>
       <c r="G13" s="8"/>
+      <c r="H13" s="15"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
       <c r="F14" s="7"/>
       <c r="G14" s="8"/>
+      <c r="H14" s="15"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="7"/>
       <c r="G15" s="8"/>
+      <c r="H15" s="15"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
       <c r="F16" s="7"/>
       <c r="G16" s="8"/>
+      <c r="H16" s="15"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
       <c r="F17" s="7"/>
       <c r="G17" s="8"/>
+      <c r="H17" s="15"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
       <c r="F18" s="7"/>
       <c r="G18" s="8"/>
+      <c r="H18" s="15"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
       <c r="F19" s="7"/>
       <c r="G19" s="8"/>
+      <c r="H19" s="15"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
       <c r="F20" s="7"/>
       <c r="G20" s="8"/>
+      <c r="H20" s="15"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="15"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
+      <c r="A21" s="16"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
       <c r="F22" s="7"/>
       <c r="G22" s="8"/>
+      <c r="H22" s="15" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
       <c r="F23" s="7"/>
       <c r="G23" s="8"/>
+      <c r="H23" s="15"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="8"/>
+      <c r="A24" s="16"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
       <c r="F25" s="7"/>
       <c r="G25" s="8"/>
+      <c r="H25" s="15" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B26" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="11"/>
+      <c r="A26" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="15"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="8"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="8"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="A28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="15"/>
+    </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="21"/>
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" s="21"/>
-      <c r="C32" s="21"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="21"/>
-    </row>
+      <c r="A30" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="15"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="15"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="21"/>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="21"/>
-      <c r="B34" s="21"/>
-      <c r="C34" s="21"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="21"/>
-    </row>
+      <c r="A33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="21"/>
-      <c r="B35" s="21"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="21"/>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="A35" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="23"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="23"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="23"/>
+      <c r="B37" s="23"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="23"/>
+      <c r="B38" s="23"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
+    </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -929,14 +1018,23 @@
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="8">
     <mergeCell ref="B1:F1"/>
+    <mergeCell ref="H2:H4"/>
     <mergeCell ref="B4:F4"/>
+    <mergeCell ref="H6:H20"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="H28:H31"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.39375" right="0.274305555555556" top="0.39375" bottom="0.39375" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="137" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="127" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/service/templates/Report_simple.xlsx
+++ b/service/templates/Report_simple.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Лист1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Лист1!$A$1:$H$38</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Лист1!$A$1:$H$37</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="37">
   <si>
     <t xml:space="preserve">Проект</t>
   </si>
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Основная сборка проекта</t>
   </si>
   <si>
-    <t xml:space="preserve">Подготовка</t>
+    <t xml:space="preserve">Сетап</t>
   </si>
   <si>
     <t xml:space="preserve">Анализ SonarQube и правка замечаний</t>
@@ -103,7 +103,7 @@
     <t xml:space="preserve">Повторная сборка, обновление данных для документации</t>
   </si>
   <si>
-    <t xml:space="preserve">Доки</t>
+    <t xml:space="preserve">Doc</t>
   </si>
   <si>
     <t xml:space="preserve">Тестовый деплой документации</t>
@@ -112,7 +112,7 @@
     <t xml:space="preserve">Смена тега в драфте</t>
   </si>
   <si>
-    <t xml:space="preserve">Теги</t>
+    <t xml:space="preserve">Тег</t>
   </si>
   <si>
     <t xml:space="preserve">Melezh</t>
@@ -122,9 +122,6 @@
   </si>
   <si>
     <t xml:space="preserve">Релиз</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Опубликовать релиз GitHub</t>
   </si>
   <si>
     <t xml:space="preserve">Обновление Readme (RU)</t>
@@ -319,7 +316,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="255" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -343,7 +340,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="255" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -502,7 +499,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.49"/>
@@ -511,7 +508,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="4.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="4.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="4.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="17.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="14.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="13.35"/>
@@ -861,7 +858,7 @@
       <c r="E25" s="6"/>
       <c r="F25" s="7"/>
       <c r="G25" s="8"/>
-      <c r="H25" s="15" t="s">
+      <c r="H25" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -877,7 +874,7 @@
       <c r="E26" s="6"/>
       <c r="F26" s="7"/>
       <c r="G26" s="8"/>
-      <c r="H26" s="15"/>
+      <c r="H26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="19"/>
@@ -900,23 +897,23 @@
       <c r="E28" s="11"/>
       <c r="F28" s="21"/>
       <c r="G28" s="22"/>
-      <c r="H28" s="15" t="s">
+      <c r="H28" s="9" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="15"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="9"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
@@ -930,36 +927,31 @@
       <c r="E30" s="6"/>
       <c r="F30" s="7"/>
       <c r="G30" s="8"/>
-      <c r="H30" s="15"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B31" s="5" t="s">
+      <c r="H30" s="9"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="15"/>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
+      <c r="B32" s="23"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="B34" s="23"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+    </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="A35" s="23"/>
       <c r="B35" s="23"/>
       <c r="C35" s="23"/>
       <c r="D35" s="23"/>
@@ -985,19 +977,11 @@
       <c r="F37" s="23"/>
       <c r="G37" s="23"/>
     </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="23"/>
-      <c r="B38" s="23"/>
-      <c r="C38" s="23"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="23"/>
-    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -1020,7 +1004,6 @@
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B1:F1"/>
@@ -1030,7 +1013,7 @@
     <mergeCell ref="H22:H23"/>
     <mergeCell ref="H25:H26"/>
     <mergeCell ref="A27:G27"/>
-    <mergeCell ref="H28:H31"/>
+    <mergeCell ref="H28:H30"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.39375" right="0.274305555555556" top="0.39375" bottom="0.39375" header="0.511811023622047" footer="0.511811023622047"/>

--- a/service/templates/Report_simple.xlsx
+++ b/service/templates/Report_simple.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Лист1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Лист1!$A$1:$H$37</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Лист1!$A$1:$H$38</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="38">
   <si>
     <t xml:space="preserve">Проект</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t xml:space="preserve">Запустить Общее | Полное обновление и сборка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обновить компоненты на клиенте</t>
   </si>
   <si>
     <t xml:space="preserve">Тестирование 1С (RU)</t>
@@ -279,7 +282,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -329,6 +332,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -499,7 +510,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.49"/>
@@ -578,43 +589,43 @@
       <c r="H4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
+      <c r="A5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="15" t="s">
-        <v>10</v>
-      </c>
+      <c r="A6" s="15"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="7"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="15"/>
+      <c r="H7" s="17" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
@@ -628,7 +639,7 @@
       <c r="E8" s="6"/>
       <c r="F8" s="7"/>
       <c r="G8" s="8"/>
-      <c r="H8" s="15"/>
+      <c r="H8" s="17"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
@@ -642,7 +653,7 @@
       <c r="E9" s="6"/>
       <c r="F9" s="7"/>
       <c r="G9" s="8"/>
-      <c r="H9" s="15"/>
+      <c r="H9" s="17"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
@@ -656,7 +667,7 @@
       <c r="E10" s="6"/>
       <c r="F10" s="7"/>
       <c r="G10" s="8"/>
-      <c r="H10" s="15"/>
+      <c r="H10" s="17"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
@@ -670,7 +681,7 @@
       <c r="E11" s="6"/>
       <c r="F11" s="7"/>
       <c r="G11" s="8"/>
-      <c r="H11" s="15"/>
+      <c r="H11" s="17"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
@@ -684,7 +695,7 @@
       <c r="E12" s="6"/>
       <c r="F12" s="7"/>
       <c r="G12" s="8"/>
-      <c r="H12" s="15"/>
+      <c r="H12" s="17"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
@@ -698,7 +709,7 @@
       <c r="E13" s="6"/>
       <c r="F13" s="7"/>
       <c r="G13" s="8"/>
-      <c r="H13" s="15"/>
+      <c r="H13" s="17"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
@@ -712,7 +723,7 @@
       <c r="E14" s="6"/>
       <c r="F14" s="7"/>
       <c r="G14" s="8"/>
-      <c r="H14" s="15"/>
+      <c r="H14" s="17"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
@@ -726,7 +737,7 @@
       <c r="E15" s="6"/>
       <c r="F15" s="7"/>
       <c r="G15" s="8"/>
-      <c r="H15" s="15"/>
+      <c r="H15" s="17"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
@@ -740,7 +751,7 @@
       <c r="E16" s="6"/>
       <c r="F16" s="7"/>
       <c r="G16" s="8"/>
-      <c r="H16" s="15"/>
+      <c r="H16" s="17"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
@@ -754,7 +765,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="7"/>
       <c r="G17" s="8"/>
-      <c r="H17" s="15"/>
+      <c r="H17" s="17"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
@@ -768,7 +779,7 @@
       <c r="E18" s="6"/>
       <c r="F18" s="7"/>
       <c r="G18" s="8"/>
-      <c r="H18" s="15"/>
+      <c r="H18" s="17"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
@@ -782,7 +793,7 @@
       <c r="E19" s="6"/>
       <c r="F19" s="7"/>
       <c r="G19" s="8"/>
-      <c r="H19" s="15"/>
+      <c r="H19" s="17"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
@@ -796,124 +807,124 @@
       <c r="E20" s="6"/>
       <c r="F20" s="7"/>
       <c r="G20" s="8"/>
-      <c r="H20" s="15"/>
+      <c r="H20" s="17"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="16"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
+      <c r="A21" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="17"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="15" t="s">
-        <v>26</v>
-      </c>
+      <c r="A22" s="18"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
       <c r="F23" s="7"/>
       <c r="G23" s="8"/>
-      <c r="H23" s="15"/>
+      <c r="H23" s="17" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="16"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
+      <c r="A24" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="17"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="9" t="s">
-        <v>29</v>
-      </c>
+      <c r="A25" s="18"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
       <c r="F26" s="7"/>
       <c r="G26" s="8"/>
-      <c r="H26" s="9"/>
+      <c r="H26" s="9" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
+      <c r="A27" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="9"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B28" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="9" t="s">
+      <c r="B29" s="22" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B29" s="5" t="s">
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="9"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
@@ -929,59 +940,72 @@
       <c r="G30" s="8"/>
       <c r="H30" s="9"/>
     </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="23"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="23"/>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="9"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="23"/>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="23"/>
-    </row>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="23"/>
-      <c r="B35" s="23"/>
-      <c r="C35" s="23"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="23"/>
+      <c r="A35" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="25"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="23"/>
-      <c r="B36" s="23"/>
-      <c r="C36" s="23"/>
-      <c r="D36" s="23"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="23"/>
+      <c r="A36" s="25"/>
+      <c r="B36" s="25"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="25"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="23"/>
-      <c r="B37" s="23"/>
-      <c r="C37" s="23"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="A37" s="25"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="25"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
+    </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -1004,16 +1028,17 @@
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="B4:F4"/>
-    <mergeCell ref="H6:H20"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="H28:H30"/>
+    <mergeCell ref="H7:H21"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="H29:H31"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.39375" right="0.274305555555556" top="0.39375" bottom="0.39375" header="0.511811023622047" footer="0.511811023622047"/>
